--- a/PTBR/Lang/PTBR/Dialog/Drama/guild_master_fighter.xlsx
+++ b/PTBR/Lang/PTBR/Dialog/Drama/guild_master_fighter.xlsx
@@ -439,7 +439,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Somente os corajosos podem realmente conhecer a derrota. Somente aqueles que conhecem o peso da espada podem encontrar o caminho para sobreviver.</t>
+          <t>Só os bravos conhecem a verdadeira derrota. Só os que sentem o peso da espada encontram o caminho para sobreviver.</t>
         </is>
       </c>
     </row>
